--- a/XLibur.Tests/Resource/Examples/Misc/Hyperlinks.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/Hyperlinks.xlsx
@@ -509,15 +509,15 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink ref="A1" r:id="rId13"/>
-    <x:hyperlink ref="A2" r:id="rId14" tooltip="Click to go to Yahoo!"/>
+    <x:hyperlink ref="A1" r:id="rId6"/>
+    <x:hyperlink ref="A2" r:id="rId7" tooltip="Click to go to Yahoo!"/>
     <x:hyperlink ref="A3" location="Hyperlinks!Test.xlsx" display="Link to a file - same folder"/>
-    <x:hyperlink ref="A4" r:id="rId15"/>
-    <x:hyperlink ref="A5" r:id="rId16"/>
+    <x:hyperlink ref="A4" r:id="rId8"/>
+    <x:hyperlink ref="A5" r:id="rId9"/>
     <x:hyperlink ref="A6" location="Hyperlinks!B1" display="Link to an address in this worksheet"/>
     <x:hyperlink ref="A7" location="'Second Sheet'!A1" display="Link to an address in another worksheet"/>
     <x:hyperlink ref="A8" location="Hyperlinks!B1:C2" tooltip="SquareBox" display="Link to a range in this worksheet"/>
-    <x:hyperlink ref="A9" r:id="rId17"/>
+    <x:hyperlink ref="A9" r:id="rId10"/>
     <x:hyperlink ref="A11" location="Hyperlinks!B1:C2" display="Odd looking link"/>
   </x:hyperlinks>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>

--- a/XLibur.Tests/Resource/Examples/Misc/Hyperlinks.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/Hyperlinks.xlsx
@@ -425,13 +425,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:A16"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="38.996339" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="38.996339" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:1">
@@ -480,7 +477,7 @@
       </x:c>
     </x:row>
     <x:row r="10" spans="1:1">
-      <x:c r="A10" s="0" t="s">
+      <x:c r="A10" t="s">
         <x:v>9</x:v>
       </x:c>
     </x:row>
@@ -490,19 +487,19 @@
       </x:c>
     </x:row>
     <x:row r="12" spans="1:1">
-      <x:c r="A12" s="0" t="str">
+      <x:c r="A12" t="str">
         <x:f>HYPERLINK("mailto:test@test.com", "Send Email through formula")</x:f>
         <x:v>Send Email through formula</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:1">
-      <x:c r="A13" s="0" t="str">
+      <x:c r="A13" t="str">
         <x:f>HYPERLINK("[Hyperlinks.xlsx]Hyperlinks!B2:C4", "Link to range through formula")</x:f>
         <x:v>Link to range through formula</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:1">
-      <x:c r="A14" s="0" t="str">
+      <x:c r="A14" t="str">
         <x:f>HYPERLINK("[../Test.xlsx]Sheet1!B2:C4", "Link to another file through formula")</x:f>
         <x:v>Link to another file through formula</x:v>
       </x:c>
@@ -520,26 +517,15 @@
     <x:hyperlink ref="A9" r:id="rId10"/>
     <x:hyperlink ref="A11" location="Hyperlinks!B1:C2" display="Odd looking link"/>
   </x:hyperlinks>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData/>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
--- a/XLibur.Tests/Resource/Examples/Misc/Hyperlinks.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/Hyperlinks.xlsx
@@ -428,7 +428,7 @@
   <x:dimension ref="A1:A16"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="38.996339" customWidth="1"/>
+    <x:col min="1" max="1" width="37.996339" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:1">

--- a/XLibur.Tests/Resource/Examples/Misc/Hyperlinks.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/Hyperlinks.xlsx
@@ -428,7 +428,7 @@
   <x:dimension ref="A1:A16"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="37.996339" customWidth="1"/>
+    <x:col min="1" max="1" width="38" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:1">
